--- a/MasterList.xlsx
+++ b/MasterList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf057eb7a9b70b82/Desktop/Projects/00_DataAnalysis_andAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="11_F25DC773A252ABDACC104861B19C55225ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D8D36C0-3D1D-41EF-BD41-89930B76F4FE}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="11_F25DC773A252ABDACC104861B19C55225ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{313F452D-A0FE-40E7-AAE8-635DB1C0169C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14370" yWindow="4320" windowWidth="19860" windowHeight="12180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="357">
   <si>
     <t>Community_Safety_Indicators</t>
   </si>
@@ -240,21 +240,6 @@
   </si>
   <si>
     <t>construction2025.csv</t>
-  </si>
-  <si>
-    <t>housing2020.csv</t>
-  </si>
-  <si>
-    <t>housing2021.csv</t>
-  </si>
-  <si>
-    <t>housing2022.csv</t>
-  </si>
-  <si>
-    <t>housing2023.csv</t>
-  </si>
-  <si>
-    <t>housing2024.csv</t>
   </si>
   <si>
     <t>housing2025.csv</t>
@@ -597,21 +582,6 @@
   </si>
   <si>
     <t>df17</t>
-  </si>
-  <si>
-    <t>df18</t>
-  </si>
-  <si>
-    <t>df19</t>
-  </si>
-  <si>
-    <t>df20</t>
-  </si>
-  <si>
-    <t>df21</t>
-  </si>
-  <si>
-    <t>df22</t>
   </si>
   <si>
     <t>df23</t>
@@ -1341,6 +1311,36 @@
   </si>
   <si>
     <t>df93</t>
+  </si>
+  <si>
+    <t>city-wards-data-4326.geojson</t>
+  </si>
+  <si>
+    <t>Neighbourhoods - historical 140 - 4326.geojson</t>
+  </si>
+  <si>
+    <t>voting-subdivisions-2022 - 4326.geojson</t>
+  </si>
+  <si>
+    <t>https://open.toronto.ca/dataset/elections-subdivisions/</t>
+  </si>
+  <si>
+    <t>https://data.urbandatacentre.ca/en/catalogue/city-toronto-city-wards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polygon shapefiles that depicts the Election Polling Subdivisions for the 2023 Mayoral By-election, 2022, 2018, 2014, 2010 and 2006 General Municipal Elections for the City of Toronto. The files work well with the GCC Centreline file and the address points file.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current boundaries for the City of Toronto's 44 municipal wards that are in effect until November 30, 2018.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The neighbourhood profiles were developed to help government and community agencies with their local planning, by providing socio-economic data at a meaningful geographic area. Unlike other geographies like wards or dissemination blocks, the boundaries of these social planning neighbourhoods change very infrequently over time, allowing researchers to perform longitudinal studies to see the changes in each area. Not all people define neighbourhoods the same way, but for the purposes of statistical reporting these neighbourhoods were defined based on Statistics Canada census tracts.
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3600B7-6010-4EDC-B261-9792DB122E94}">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.28515625" bestFit="1" customWidth="1"/>
@@ -1750,143 +1750,149 @@
         <v>49</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>222</v>
+        <v>352</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>349</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>106</v>
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="E3" t="s">
-        <v>132</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>350</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>107</v>
+        <v>351</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="405" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>108</v>
+        <v>193</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="345" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="225" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="E7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="405" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="E8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="345" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1894,14 +1900,14 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1909,14 +1915,14 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1924,14 +1930,14 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1939,14 +1945,14 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1954,14 +1960,14 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1969,14 +1975,14 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1984,14 +1990,14 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -1999,14 +2005,14 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2014,14 +2020,14 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2029,14 +2035,14 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2044,14 +2050,14 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2059,14 +2065,14 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2074,14 +2080,14 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2089,14 +2095,14 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -2104,112 +2110,112 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="345" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
-        <v>76</v>
-      </c>
       <c r="C29" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>112</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D29" s="3"/>
       <c r="E29" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="345" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>113</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="E30" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2217,14 +2223,14 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2232,1084 +2238,1054 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="180" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
         <v>80</v>
       </c>
-      <c r="C33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" s="3"/>
-      <c r="E33" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="C36" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" t="s">
         <v>81</v>
       </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="3"/>
-      <c r="E34" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="180" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="C37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
         <v>82</v>
       </c>
-      <c r="C35" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="3" t="s">
+      <c r="C38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E35" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="E38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
         <v>83</v>
       </c>
-      <c r="C36" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="3" t="s">
+      <c r="C39" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="E39" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="285" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" t="s">
         <v>87</v>
       </c>
-      <c r="C40" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="3" t="s">
+      <c r="C43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E43" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="270" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E45" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E46" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" t="s">
+    <row r="49" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" t="s">
+    <row r="50" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E43" t="s">
+    <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" ht="285" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>18</v>
-      </c>
-      <c r="B44" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="B51" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" ht="270" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>19</v>
-      </c>
-      <c r="B45" t="s">
-        <v>92</v>
-      </c>
-      <c r="C45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="C51" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="270" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="D51" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E51" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="C52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E52" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" t="s">
-        <v>46</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>24</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>25</v>
-      </c>
-      <c r="B52" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>182</v>
-      </c>
-      <c r="B53" t="s">
-        <v>183</v>
-      </c>
       <c r="C53" t="s">
-        <v>184</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>204</v>
+        <v>174</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="E53" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C54" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E54" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E55" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" t="s">
+        <v>179</v>
+      </c>
+      <c r="C56" t="s">
+        <v>174</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E56" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E57" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" t="s">
+        <v>181</v>
+      </c>
+      <c r="C58" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" t="s">
         <v>182</v>
       </c>
-      <c r="B55" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" t="s">
-        <v>184</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="E55" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>182</v>
-      </c>
-      <c r="B56" t="s">
-        <v>187</v>
-      </c>
-      <c r="C56" t="s">
-        <v>184</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="E56" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>182</v>
-      </c>
-      <c r="B57" t="s">
-        <v>188</v>
-      </c>
-      <c r="C57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E57" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>182</v>
-      </c>
-      <c r="B58" t="s">
-        <v>189</v>
-      </c>
-      <c r="C58" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E58" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>182</v>
-      </c>
-      <c r="B59" t="s">
-        <v>190</v>
-      </c>
       <c r="C59" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>210</v>
+        <v>174</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C60" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E60" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" t="s">
         <v>184</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="E60" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>182</v>
-      </c>
-      <c r="B61" t="s">
-        <v>192</v>
-      </c>
       <c r="C61" t="s">
-        <v>184</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>212</v>
+        <v>174</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="E61" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C62" t="s">
+        <v>174</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E62" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>172</v>
+      </c>
+      <c r="B63" t="s">
         <v>184</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E62" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>182</v>
-      </c>
-      <c r="B63" t="s">
-        <v>194</v>
-      </c>
       <c r="C63" t="s">
-        <v>184</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>223</v>
+        <v>174</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="E63" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C64" t="s">
-        <v>184</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>215</v>
+        <v>174</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B65" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C65" t="s">
-        <v>184</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>214</v>
+        <v>174</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>207</v>
       </c>
       <c r="E65" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C66" t="s">
-        <v>184</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>216</v>
+        <v>174</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>208</v>
       </c>
       <c r="E66" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B67" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s">
-        <v>184</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>217</v>
+        <v>174</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="E67" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B68" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C68" t="s">
-        <v>184</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>218</v>
+        <v>174</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="E68" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B69" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C69" t="s">
-        <v>184</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>219</v>
+        <v>174</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="E69" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" t="s">
+        <v>235</v>
+      </c>
+      <c r="C70" t="s">
+        <v>236</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E70" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="330" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" t="s">
+        <v>238</v>
+      </c>
+      <c r="C71" t="s">
+        <v>239</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="E71" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>182</v>
-      </c>
-      <c r="B70" t="s">
-        <v>199</v>
-      </c>
-      <c r="C70" t="s">
-        <v>184</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="B72" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>182</v>
-      </c>
-      <c r="B71" t="s">
-        <v>200</v>
-      </c>
-      <c r="C71" t="s">
-        <v>184</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="C72" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="D72" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E72" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="360" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>243</v>
+      </c>
+      <c r="B73" t="s">
         <v>244</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C73" t="s">
         <v>245</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D73" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E73" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="195" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>246</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E72" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="330" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B74" t="s">
         <v>247</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C74" t="s">
         <v>248</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D74" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E74" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>249</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E73" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B75" t="s">
         <v>250</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C75" t="s">
         <v>251</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D75" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E75" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>252</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E74" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="360" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="B76" t="s">
         <v>253</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C76" t="s">
         <v>254</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D76" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E76" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>255</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E75" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="195" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B77" t="s">
         <v>256</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C77" t="s">
         <v>257</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D77" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="E77" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="405" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>258</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E76" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="B78" t="s">
         <v>259</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C78" t="s">
         <v>260</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D78" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E78" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="210" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>261</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E77" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B79" t="s">
         <v>262</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C79" t="s">
         <v>263</v>
       </c>
-      <c r="C78" t="s">
-        <v>264</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E78" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>265</v>
-      </c>
-      <c r="B79" t="s">
-        <v>266</v>
-      </c>
-      <c r="C79" t="s">
-        <v>267</v>
-      </c>
       <c r="D79" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E79" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="405" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>264</v>
+      </c>
+      <c r="B80" t="s">
+        <v>265</v>
+      </c>
+      <c r="C80" t="s">
+        <v>266</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E80" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>267</v>
+      </c>
+      <c r="B81" t="s">
         <v>268</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C81" t="s">
         <v>269</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D81" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E81" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>270</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E80" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="210" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B82" t="s">
         <v>271</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C82" t="s">
         <v>272</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D82" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E82" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>273</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E81" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="405" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="B83" t="s">
         <v>274</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C83" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D83" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E83" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>276</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E82" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B84" t="s">
         <v>277</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C84" t="s">
         <v>278</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D84" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E84" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>276</v>
+      </c>
+      <c r="B85" t="s">
         <v>279</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E83" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="C85" t="s">
+        <v>278</v>
+      </c>
+      <c r="E85" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="225" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>280</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B86" t="s">
         <v>281</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C86" t="s">
         <v>282</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E84" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>283</v>
-      </c>
-      <c r="B85" t="s">
-        <v>284</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E85" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="105" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>286</v>
-      </c>
-      <c r="B86" t="s">
-        <v>287</v>
-      </c>
-      <c r="C86" t="s">
-        <v>288</v>
-      </c>
       <c r="D86" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="E86" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>280</v>
+      </c>
+      <c r="B87" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" t="s">
+        <v>282</v>
+      </c>
+      <c r="E87" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>284</v>
+      </c>
+      <c r="B88" t="s">
+        <v>285</v>
+      </c>
+      <c r="C88" t="s">
         <v>286</v>
       </c>
-      <c r="B87" t="s">
+      <c r="D88" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E88" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>287</v>
+      </c>
+      <c r="B89" t="s">
+        <v>288</v>
+      </c>
+      <c r="C89" t="s">
         <v>289</v>
       </c>
-      <c r="C87" t="s">
-        <v>288</v>
-      </c>
-      <c r="E87" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="225" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="D89" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E89" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="405" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>290</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B90" t="s">
         <v>291</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C90" t="s">
         <v>292</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E88" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>290</v>
-      </c>
-      <c r="B89" t="s">
-        <v>293</v>
-      </c>
-      <c r="C89" t="s">
-        <v>292</v>
-      </c>
-      <c r="E89" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>294</v>
-      </c>
-      <c r="B90" t="s">
-        <v>295</v>
-      </c>
-      <c r="C90" t="s">
-        <v>296</v>
-      </c>
       <c r="D90" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="E90" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>293</v>
+      </c>
+      <c r="B91" t="s">
+        <v>294</v>
+      </c>
+      <c r="C91" t="s">
+        <v>295</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="E91" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>296</v>
+      </c>
+      <c r="B92" t="s">
         <v>297</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C92" t="s">
         <v>298</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D92" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E92" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="285" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>299</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="E91" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="405" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="B93" t="s">
         <v>300</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C93" t="s">
         <v>301</v>
       </c>
-      <c r="C92" t="s">
-        <v>302</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E92" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>303</v>
-      </c>
-      <c r="B93" t="s">
-        <v>304</v>
-      </c>
-      <c r="C93" t="s">
-        <v>305</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E93" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>306</v>
-      </c>
-      <c r="B94" t="s">
-        <v>307</v>
-      </c>
-      <c r="C94" t="s">
-        <v>308</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E94" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="285" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>309</v>
-      </c>
-      <c r="B95" t="s">
-        <v>310</v>
-      </c>
-      <c r="C95" t="s">
-        <v>311</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E95" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C42" r:id="rId1" xr:uid="{8EDF15DB-5FF8-47DD-AF4F-2EC086296954}"/>
-    <hyperlink ref="C49" r:id="rId2" xr:uid="{3FEECFB9-6A26-4A52-B63B-0567CDE56063}"/>
-    <hyperlink ref="C43" r:id="rId3" xr:uid="{B2A08AE1-906F-4CB5-9D5A-5716417D5A56}"/>
-    <hyperlink ref="C85" r:id="rId4" xr:uid="{EDA25EDE-B74A-4B5A-9EDF-3380AC05D8B3}"/>
+    <hyperlink ref="C40" r:id="rId1" xr:uid="{8EDF15DB-5FF8-47DD-AF4F-2EC086296954}"/>
+    <hyperlink ref="C47" r:id="rId2" xr:uid="{3FEECFB9-6A26-4A52-B63B-0567CDE56063}"/>
+    <hyperlink ref="C41" r:id="rId3" xr:uid="{B2A08AE1-906F-4CB5-9D5A-5716417D5A56}"/>
+    <hyperlink ref="C83" r:id="rId4" xr:uid="{EDA25EDE-B74A-4B5A-9EDF-3380AC05D8B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
